--- a/informes_data/Euroleague/2025-26/playoffs/individual/NP_play_by_play_EL_386_R41.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/individual/NP_play_by_play_EL_386_R41.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C. OKEKE</t>
+          <t>T. MALEDON</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.7514</v>
+        <v>3.3317</v>
       </c>
       <c r="E2" t="n">
-        <v>5.3702</v>
+        <v>2.8819</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3812</v>
+        <v>0.4498</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3158</v>
+        <v>-0.1801</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6909</v>
+        <v>0.7074</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3751</v>
+        <v>-0.8874</v>
       </c>
       <c r="J2" t="n">
-        <v>1.419</v>
+        <v>0.8606</v>
       </c>
       <c r="K2" t="n">
-        <v>1.6716</v>
+        <v>0.4467</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.2526</v>
+        <v>0.4138</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.1033</v>
+        <v>-1.0406</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.9808</v>
+        <v>0.2607</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.1225</v>
+        <v>-1.3013</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9099</v>
+        <v>1.1374</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9099</v>
+        <v>1.1374</v>
       </c>
       <c r="S2" t="n">
-        <v>3.7523</v>
+        <v>0.7393</v>
       </c>
       <c r="T2" t="n">
-        <v>3.9512</v>
+        <v>0.3862</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1988</v>
+        <v>0.3531</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7734</v>
+        <v>1.6352</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.6352</v>
       </c>
       <c r="X2" t="n">
-        <v>0.7734</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T. LYLES</t>
+          <t>C. OKEKE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2923</v>
+        <v>3.2802</v>
       </c>
       <c r="E3" t="n">
-        <v>1.0842</v>
+        <v>2.802</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2081</v>
+        <v>0.4782</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.567</v>
+        <v>0.3158</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.3674</v>
+        <v>0.6909</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1995</v>
+        <v>-0.3751</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.787</v>
+        <v>1.419</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.5775</v>
+        <v>1.6716</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7904</v>
+        <v>-0.2526</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.78</v>
+        <v>-1.1033</v>
       </c>
       <c r="N3" t="n">
-        <v>0.21</v>
+        <v>-0.9808</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.99</v>
+        <v>-0.1225</v>
       </c>
       <c r="P3" t="n">
-        <v>2.0473</v>
+        <v>0.9099</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0473</v>
+        <v>0.9099</v>
       </c>
       <c r="S3" t="n">
-        <v>1.5636</v>
+        <v>1.2811</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6227</v>
+        <v>1.383</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9409</v>
+        <v>-0.1018</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2485</v>
+        <v>0.7734</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2485</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.7734</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T. MALEDON</t>
+          <t>T. LYLES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4176</v>
+        <v>2.8003</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0648</v>
+        <v>0.8507</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3529</v>
+        <v>1.9496</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1801</v>
+        <v>-1.567</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7074</v>
+        <v>-1.3674</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.8874</v>
+        <v>-0.1995</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8606</v>
+        <v>-0.787</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4467</v>
+        <v>-1.5775</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4138</v>
+        <v>0.7904</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.0406</v>
+        <v>-0.78</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2607</v>
+        <v>0.21</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.3013</v>
+        <v>-0.99</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1374</v>
+        <v>2.0473</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1374</v>
+        <v>2.0473</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1748</v>
+        <v>1.0715</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.431</v>
+        <v>0.3893</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2561</v>
+        <v>0.6823</v>
       </c>
       <c r="V4" t="n">
-        <v>1.6352</v>
+        <v>1.2485</v>
       </c>
       <c r="W4" t="n">
-        <v>1.6352</v>
+        <v>1.2485</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8266</v>
+        <v>2.6833</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0717</v>
+        <v>2.1224</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7549</v>
+        <v>0.5609</v>
       </c>
       <c r="G5" t="n">
         <v>0.5004</v>
@@ -844,13 +844,13 @@
         <v>2.0473</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.2188</v>
+        <v>-0.3621</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.4365</v>
+        <v>-0.3859</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2177</v>
+        <v>0.0238</v>
       </c>
       <c r="V5" t="n">
         <v>1.6352</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>U. GARUBA</t>
+          <t>G. DECK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3771</v>
+        <v>0.9346</v>
       </c>
       <c r="E6" t="n">
-        <v>1.0196</v>
+        <v>0.8899</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3575</v>
+        <v>0.0446</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0254</v>
+        <v>0.8478</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3953</v>
+        <v>2.7252</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.37</v>
+        <v>-1.8774</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8554</v>
+        <v>2.0721</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6691</v>
+        <v>1.9976</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1863</v>
+        <v>0.0745</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.83</v>
+        <v>-1.2243</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2738</v>
+        <v>0.7276</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5562</v>
+        <v>-1.9519</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.2275</v>
+        <v>0.2275</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.1374</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9099</v>
+        <v>1.3648</v>
       </c>
       <c r="S6" t="n">
-        <v>1.966</v>
+        <v>-0.1407</v>
       </c>
       <c r="T6" t="n">
-        <v>1.6883</v>
+        <v>-0.0448</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2777</v>
+        <v>-0.0959</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3867</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.3867</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>W. TAVARES</t>
+          <t>U. GARUBA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5367</v>
+        <v>0.6893</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4257</v>
+        <v>0.2024</v>
       </c>
       <c r="F7" t="n">
-        <v>0.111</v>
+        <v>0.4868</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3356</v>
+        <v>0.0254</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5525</v>
+        <v>0.3953</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2169</v>
+        <v>-0.37</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5693</v>
+        <v>0.8554</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5693</v>
+        <v>0.6691</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.1863</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2338</v>
+        <v>-0.83</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0169</v>
+        <v>-0.2738</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2169</v>
+        <v>-0.5562</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2275</v>
+        <v>-0.2275</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.1374</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2275</v>
+        <v>0.9099</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0264</v>
+        <v>1.2781</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1437</v>
+        <v>0.8711</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1173</v>
+        <v>0.407</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.3867</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-0.3867</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. LEN</t>
+          <t>W. TAVARES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3489</v>
+        <v>0.4074</v>
       </c>
       <c r="E8" t="n">
-        <v>1.3871</v>
+        <v>0.4257</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.0383</v>
+        <v>-0.0183</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.9809</v>
+        <v>0.3356</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.1027</v>
+        <v>0.5525</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8782</v>
+        <v>-0.2169</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.494</v>
+        <v>0.5693</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6057</v>
+        <v>0.5693</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1118</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.4869</v>
+        <v>-0.2338</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.497</v>
+        <v>-0.0169</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.99</v>
+        <v>-0.2169</v>
       </c>
       <c r="P8" t="n">
-        <v>2.0473</v>
+        <v>0.2275</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0473</v>
+        <v>0.2275</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2825</v>
+        <v>-0.1556</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2992</v>
+        <v>-0.1437</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5816</v>
+        <v>-0.012</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.1802</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.1802</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. DECK</t>
+          <t>A. LEN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2058</v>
+        <v>0.2789</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0728</v>
+        <v>1.7373</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2786</v>
+        <v>-1.4584</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8478</v>
+        <v>-1.9809</v>
       </c>
       <c r="H9" t="n">
-        <v>2.7252</v>
+        <v>-1.1027</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.8774</v>
+        <v>-0.8782</v>
       </c>
       <c r="J9" t="n">
-        <v>2.0721</v>
+        <v>-0.494</v>
       </c>
       <c r="K9" t="n">
-        <v>1.9976</v>
+        <v>-0.6057</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0745</v>
+        <v>0.1118</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.2243</v>
+        <v>-1.4869</v>
       </c>
       <c r="N9" t="n">
-        <v>0.7276</v>
+        <v>-0.497</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.9519</v>
+        <v>-0.99</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2275</v>
+        <v>2.0473</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1374</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3648</v>
+        <v>2.0473</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.281</v>
+        <v>0.2125</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8619</v>
+        <v>0.051</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4191</v>
+        <v>0.1615</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.1802</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-2.1802</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4218</v>
+        <v>-1.1758</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.9814</v>
+        <v>-1.8647</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5596</v>
+        <v>0.6889</v>
       </c>
       <c r="G10" t="n">
         <v>-0.3799</v>
@@ -1234,13 +1234,13 @@
         <v>0.6824</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4286</v>
+        <v>-0.1826</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3591</v>
+        <v>-0.2424</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.06950000000000001</v>
+        <v>0.0598</v>
       </c>
       <c r="V10" t="n">
         <v>-0.1583</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.2265</v>
+        <v>-1.1831</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.3065</v>
+        <v>-0.4893</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9201</v>
+        <v>-0.6938</v>
       </c>
       <c r="G11" t="n">
         <v>-1.3175</v>
@@ -1312,13 +1312,13 @@
         <v>0.6824</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0464</v>
+        <v>-0.003</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5746</v>
+        <v>0.2425</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4718</v>
+        <v>-0.2455</v>
       </c>
       <c r="V11" t="n">
         <v>-0.5451</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.5477</v>
+        <v>-3.3325</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.9231</v>
+        <v>-1.7402</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.6246</v>
+        <v>-1.5922</v>
       </c>
       <c r="G12" t="n">
         <v>-3.2568</v>
@@ -1390,13 +1390,13 @@
         <v>1.8198</v>
       </c>
       <c r="S12" t="n">
-        <v>1.6618</v>
+        <v>0.877</v>
       </c>
       <c r="T12" t="n">
-        <v>1.401</v>
+        <v>0.5838</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2609</v>
+        <v>0.2932</v>
       </c>
       <c r="V12" t="n">
         <v>-1.6352</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.8637</v>
+        <v>-3.429</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.039</v>
+        <v>-3.572</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1753</v>
+        <v>0.143</v>
       </c>
       <c r="G13" t="n">
         <v>-4.9032</v>
@@ -1468,13 +1468,13 @@
         <v>2.0473</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3208</v>
+        <v>0.1138</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4428</v>
+        <v>0.0241</v>
       </c>
       <c r="U13" t="n">
-        <v>0.122</v>
+        <v>0.0896</v>
       </c>
       <c r="V13" t="n">
         <v>2.7253</v>
@@ -1501,22 +1501,22 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.285100000000002</v>
+        <v>5.285300000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>4.246099999999998</v>
+        <v>4.246099999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0389</v>
+        <v>1.0391</v>
       </c>
       <c r="G14" t="n">
         <v>-11.5604</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.0813</v>
+        <v>-2.081300000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-9.478999999999999</v>
+        <v>-9.479000000000001</v>
       </c>
       <c r="J14" t="n">
         <v>1.193100000000001</v>
@@ -1546,13 +1546,13 @@
         <v>15.9233</v>
       </c>
       <c r="S14" t="n">
-        <v>4.7294</v>
+        <v>4.7293</v>
       </c>
       <c r="T14" t="n">
-        <v>3.1144</v>
+        <v>3.1142</v>
       </c>
       <c r="U14" t="n">
-        <v>1.615</v>
+        <v>1.6151</v>
       </c>
       <c r="V14" t="n">
         <v>5.2923</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>8.352600000000001</v>
+        <v>5.2962</v>
       </c>
       <c r="E15" t="n">
-        <v>8.406000000000001</v>
+        <v>6.7717</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0533</v>
+        <v>-1.4755</v>
       </c>
       <c r="G15" t="n">
         <v>5.5762</v>
@@ -1624,13 +1624,13 @@
         <v>1.3648</v>
       </c>
       <c r="S15" t="n">
-        <v>3.4334</v>
+        <v>0.377</v>
       </c>
       <c r="T15" t="n">
-        <v>2.0475</v>
+        <v>0.4133</v>
       </c>
       <c r="U15" t="n">
-        <v>1.3859</v>
+        <v>-0.0363</v>
       </c>
       <c r="V15" t="n">
         <v>-2.0219</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.8598</v>
+        <v>3.799</v>
       </c>
       <c r="E16" t="n">
-        <v>4.1491</v>
+        <v>4.7328</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.2893</v>
+        <v>-0.9337</v>
       </c>
       <c r="G16" t="n">
         <v>6.1004</v>
@@ -1702,13 +1702,13 @@
         <v>1.3648</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.6483</v>
+        <v>-1.7091</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.0654</v>
+        <v>-0.4817</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.5829</v>
+        <v>-1.2274</v>
       </c>
       <c r="V16" t="n">
         <v>0.5451</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.3366</v>
+        <v>3.5667</v>
       </c>
       <c r="E17" t="n">
-        <v>2.1791</v>
+        <v>2.7628</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1575</v>
+        <v>0.8038999999999999</v>
       </c>
       <c r="G17" t="n">
         <v>4.5368</v>
@@ -1780,13 +1780,13 @@
         <v>1.5923</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.586</v>
+        <v>-1.3559</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8379</v>
+        <v>-0.2542</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.7481</v>
+        <v>-1.1017</v>
       </c>
       <c r="V17" t="n">
         <v>0.1583</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9855</v>
+        <v>0.9209000000000001</v>
       </c>
       <c r="E18" t="n">
         <v>-0.2355</v>
       </c>
       <c r="F18" t="n">
-        <v>1.221</v>
+        <v>1.1564</v>
       </c>
       <c r="G18" t="n">
         <v>0.6575</v>
@@ -1858,13 +1858,13 @@
         <v>0.4549</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1269</v>
+        <v>-0.1916</v>
       </c>
       <c r="T18" t="n">
         <v>-0.2873</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1604</v>
+        <v>0.09569999999999999</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3179</v>
+        <v>-0.6445</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1317</v>
+        <v>0.4819</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.4496</v>
+        <v>-1.1264</v>
       </c>
       <c r="G19" t="n">
         <v>0.0117</v>
@@ -1936,13 +1936,13 @@
         <v>1.3648</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.6043</v>
+        <v>-0.9308999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7781</v>
+        <v>-0.4279</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.8262</v>
+        <v>-0.503</v>
       </c>
       <c r="V19" t="n">
         <v>-1.0901</v>
@@ -1969,10 +1969,10 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6878</v>
+        <v>-1.5711</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.393</v>
+        <v>-0.2762</v>
       </c>
       <c r="F20" t="n">
         <v>-1.2949</v>
@@ -2014,10 +2014,10 @@
         <v>0.4549</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1437</v>
+        <v>-0.0269</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3471</v>
+        <v>-0.2304</v>
       </c>
       <c r="U20" t="n">
         <v>0.2035</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.2897</v>
+        <v>-2.3543</v>
       </c>
       <c r="E22" t="n">
         <v>-2.01</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.2797</v>
+        <v>-0.3443</v>
       </c>
       <c r="G22" t="n">
         <v>-1.181</v>
@@ -2170,13 +2170,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0287</v>
+        <v>-0.0359</v>
       </c>
       <c r="T22" t="n">
         <v>-0.1317</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1604</v>
+        <v>0.09569999999999999</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.8866</v>
+        <v>-3.4829</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.3882</v>
+        <v>-2.8551</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.4984</v>
+        <v>-0.6277</v>
       </c>
       <c r="G23" t="n">
         <v>2.5455</v>
@@ -2248,13 +2248,13 @@
         <v>1.1374</v>
       </c>
       <c r="S23" t="n">
-        <v>1.0272</v>
+        <v>0.431</v>
       </c>
       <c r="T23" t="n">
-        <v>0.7185</v>
+        <v>0.2516</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3086</v>
+        <v>0.1794</v>
       </c>
       <c r="V23" t="n">
         <v>-0.5451</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.3605</v>
+        <v>-3.8236</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.9417</v>
+        <v>-2.825</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.4188</v>
+        <v>-0.9986</v>
       </c>
       <c r="G24" t="n">
         <v>-3.5393</v>
@@ -2326,13 +2326,13 @@
         <v>0.2275</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8213</v>
+        <v>-0.2843</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0119</v>
+        <v>0.1049</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.8094</v>
+        <v>-0.3892</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.0035</v>
+        <v>-4.718</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.6261</v>
+        <v>-4.2759</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.3774</v>
+        <v>-0.4421</v>
       </c>
       <c r="G25" t="n">
         <v>-2.6737</v>
@@ -2404,13 +2404,13 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.0551</v>
+        <v>0.2305</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.419</v>
+        <v>-0.0688</v>
       </c>
       <c r="U25" t="n">
-        <v>0.3639</v>
+        <v>0.2992</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,10 +2437,10 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.285099999999999</v>
+        <v>-5.2852</v>
       </c>
       <c r="E26" t="n">
-        <v>0.05100000000000016</v>
+        <v>0.05110000000000081</v>
       </c>
       <c r="F26" t="n">
         <v>-5.3361</v>
@@ -2482,13 +2482,13 @@
         <v>9.098799999999999</v>
       </c>
       <c r="S26" t="n">
-        <v>-4.729500000000001</v>
+        <v>-4.7293</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.6152</v>
+        <v>-1.615</v>
       </c>
       <c r="U26" t="n">
-        <v>-3.1143</v>
+        <v>-3.1145</v>
       </c>
       <c r="V26" t="n">
         <v>-5.292299999999999</v>
